--- a/output/daily_ratings/uk_ratings_2026-06-09.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-06-09.xlsx
@@ -524,34 +524,36 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Almavillalobas</t>
+          <t>Barnsnape Boy</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>85.61</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>54.3</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-8.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="3">
@@ -580,34 +582,38 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Voodoo Ray (IRE)</t>
+          <t>Rainbow Sign</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M3" t="n">
         <v>85.61</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>52.9</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>-8.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="4">
@@ -636,28 +642,30 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Barnsnape Boy</t>
+          <t>Fai Fai</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>135</v>
       </c>
       <c r="K4" t="n">
-        <v>48</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.25</v>
+      </c>
       <c r="M4" t="n">
         <v>85.61</v>
       </c>
       <c r="N4" t="n">
-        <v>57.9</v>
+        <v>56.9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -665,7 +673,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -694,11 +702,11 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Rainbow Sign</t>
+          <t>Embarked (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -708,16 +716,16 @@
         <v>135</v>
       </c>
       <c r="K5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
         <v>85.61</v>
       </c>
       <c r="N5" t="n">
-        <v>56.6</v>
+        <v>55.5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -725,7 +733,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -754,30 +762,30 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fai Fai</t>
+          <t>Mokata</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="K6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="M6" t="n">
         <v>85.61</v>
       </c>
       <c r="N6" t="n">
-        <v>56.9</v>
+        <v>47.4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -785,7 +793,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -814,30 +822,30 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Embarked (IRE)</t>
+          <t>Horus</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
         <v>85.61</v>
       </c>
       <c r="N7" t="n">
-        <v>55.5</v>
+        <v>44.3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -873,40 +881,24 @@
       <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Mokata</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>125</v>
-      </c>
-      <c r="K8" t="n">
-        <v>49</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="M8" t="n">
-        <v>85.61</v>
-      </c>
-      <c r="N8" t="n">
-        <v>49.2</v>
-      </c>
+          <t>Almavillalobas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -933,40 +925,24 @@
       <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Horus</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>135</v>
-      </c>
-      <c r="K9" t="n">
-        <v>47</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>85.61</v>
-      </c>
-      <c r="N9" t="n">
-        <v>50.9</v>
-      </c>
+          <t>Voodoo Ray (IRE)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1167,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K13" t="n">
         <v>50</v>
@@ -1179,7 +1155,7 @@
         <v>63.34</v>
       </c>
       <c r="N13" t="n">
-        <v>62.7</v>
+        <v>57.9</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1187,7 +1163,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1227,7 +1203,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K14" t="n">
         <v>43</v>
@@ -1239,7 +1215,7 @@
         <v>63.34</v>
       </c>
       <c r="N14" t="n">
-        <v>62.4</v>
+        <v>57.1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1247,7 +1223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -1307,7 +1283,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1407,7 +1383,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K17" t="n">
         <v>44</v>
@@ -1419,7 +1395,7 @@
         <v>63.34</v>
       </c>
       <c r="N17" t="n">
-        <v>54.7</v>
+        <v>53.1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1467,7 +1443,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K18" t="n">
         <v>43</v>
@@ -1479,7 +1455,7 @@
         <v>63.34</v>
       </c>
       <c r="N18" t="n">
-        <v>46.2</v>
+        <v>41.9</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1527,7 +1503,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K19" t="n">
         <v>46</v>
@@ -1539,7 +1515,7 @@
         <v>63.34</v>
       </c>
       <c r="N19" t="n">
-        <v>42.6</v>
+        <v>39.7</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1576,34 +1552,36 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Astronomica</t>
+          <t>Play Me</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>96.14</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>64.8</v>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="21">
@@ -1632,28 +1610,30 @@
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Play Me</t>
+          <t>Rogue Dynasty</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K21" t="n">
-        <v>62</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M21" t="n">
         <v>96.14</v>
       </c>
       <c r="N21" t="n">
-        <v>72.8</v>
+        <v>74.5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1661,7 +1641,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1690,30 +1670,30 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Rogue Dynasty</t>
+          <t>King Of War</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K22" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
         <v>96.14</v>
       </c>
       <c r="N22" t="n">
-        <v>74.5</v>
+        <v>66</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1721,7 +1701,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1750,30 +1730,30 @@
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>King Of War</t>
+          <t>Tactical Plan</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K23" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
         <v>96.14</v>
       </c>
       <c r="N23" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1781,7 +1761,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1810,11 +1790,11 @@
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tactical Plan</t>
+          <t>Celestias Comet (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1827,13 +1807,13 @@
         <v>70</v>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
         <v>96.14</v>
       </c>
       <c r="N24" t="n">
-        <v>67.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1841,7 +1821,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1870,30 +1850,30 @@
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Celestias Comet (IRE)</t>
+          <t>Gone Rogue (IRE)</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M25" t="n">
         <v>96.14</v>
       </c>
       <c r="N25" t="n">
-        <v>62.8</v>
+        <v>52.8</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1901,7 +1881,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="26">
@@ -1930,30 +1910,30 @@
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Gone Rogue (IRE)</t>
+          <t>Lordsbridge Grey</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K26" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L26" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="M26" t="n">
         <v>96.14</v>
       </c>
       <c r="N26" t="n">
-        <v>55.6</v>
+        <v>58</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1961,7 +1941,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1990,15 +1970,15 @@
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lordsbridge Grey</t>
+          <t>Tea Sea (FR)</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
         <v>135</v>
@@ -2007,13 +1987,13 @@
         <v>70</v>
       </c>
       <c r="L27" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
         <v>96.14</v>
       </c>
       <c r="N27" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2050,30 +2030,30 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tea Sea (FR)</t>
+          <t>Gunfighter (IRE)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K28" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="M28" t="n">
         <v>96.14</v>
       </c>
       <c r="N28" t="n">
-        <v>57.4</v>
+        <v>55.4</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2110,30 +2090,30 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Gunfighter (IRE)</t>
+          <t>Blue Collar Lad</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="K29" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L29" t="n">
-        <v>9.75</v>
+        <v>13.75</v>
       </c>
       <c r="M29" t="n">
         <v>96.14</v>
       </c>
       <c r="N29" t="n">
-        <v>55.4</v>
+        <v>28.4</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2141,7 +2121,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="30">
@@ -2170,30 +2150,30 @@
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Blue Collar Lad</t>
+          <t>Amused (IRE)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="K30" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="L30" t="n">
-        <v>13.75</v>
+        <v>14.25</v>
       </c>
       <c r="M30" t="n">
         <v>96.14</v>
       </c>
       <c r="N30" t="n">
-        <v>28.4</v>
+        <v>44</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2201,7 +2181,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2230,34 +2210,34 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Amused (IRE)</t>
+          <t>Far And Above (IRE)</t>
         </is>
       </c>
       <c r="I31" t="n">
         <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K31" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L31" t="n">
-        <v>14.25</v>
+        <v>22.75</v>
       </c>
       <c r="M31" t="n">
         <v>96.14</v>
       </c>
       <c r="N31" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2289,40 +2269,24 @@
       <c r="F32" t="n">
         <v>5</v>
       </c>
-      <c r="G32" t="n">
-        <v>12</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Far And Above (IRE)</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" t="n">
-        <v>127</v>
-      </c>
-      <c r="K32" t="n">
-        <v>62</v>
-      </c>
-      <c r="L32" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="M32" t="n">
-        <v>96.14</v>
-      </c>
-      <c r="N32" t="n">
-        <v>35</v>
-      </c>
+          <t>Astronomica</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2350,34 +2314,36 @@
         <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Monks Mead</t>
+          <t>Bohemian Breeze (IRE)</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K33" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>125.52</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>65.3</v>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2406,28 +2372,30 @@
         <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bohemian Breeze (IRE)</t>
+          <t>Night Bear</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J34" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K34" t="n">
-        <v>55</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M34" t="n">
         <v>125.52</v>
       </c>
       <c r="N34" t="n">
-        <v>65.3</v>
+        <v>63.1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2464,30 +2432,30 @@
         <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Night Bear</t>
+          <t>Power Of Prayer (GER)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K35" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L35" t="n">
-        <v>0.15</v>
+        <v>2.65</v>
       </c>
       <c r="M35" t="n">
         <v>125.52</v>
       </c>
       <c r="N35" t="n">
-        <v>63.1</v>
+        <v>57.8</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2495,7 +2463,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36">
@@ -2524,30 +2492,30 @@
         <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Power Of Prayer (GER)</t>
+          <t>Little Tiger</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K36" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L36" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
         <v>125.52</v>
       </c>
       <c r="N36" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2555,7 +2523,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2584,30 +2552,30 @@
         <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Little Tiger</t>
+          <t>Turpin</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K37" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="M37" t="n">
         <v>125.52</v>
       </c>
       <c r="N37" t="n">
-        <v>60.9</v>
+        <v>57.6</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2615,7 +2583,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2644,30 +2612,30 @@
         <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Turpin</t>
+          <t>Twilight Guest</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K38" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L38" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="M38" t="n">
         <v>125.52</v>
       </c>
       <c r="N38" t="n">
-        <v>57.6</v>
+        <v>52.1</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2704,11 +2672,11 @@
         <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Twilight Guest</t>
+          <t>Foinix</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2721,13 +2689,13 @@
         <v>48</v>
       </c>
       <c r="L39" t="n">
-        <v>4.7</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>125.52</v>
       </c>
       <c r="N39" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2764,30 +2732,30 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Foinix</t>
+          <t>Masqool (IRE)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K40" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L40" t="n">
-        <v>4.85</v>
+        <v>6.350000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>125.52</v>
       </c>
       <c r="N40" t="n">
-        <v>52</v>
+        <v>50.5</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2824,30 +2792,30 @@
         <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Masqool (IRE)</t>
+          <t>Celebrating Ethel (IRE)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K41" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L41" t="n">
-        <v>6.35</v>
+        <v>7.6</v>
       </c>
       <c r="M41" t="n">
         <v>125.52</v>
       </c>
       <c r="N41" t="n">
-        <v>50.5</v>
+        <v>37.7</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2855,7 +2823,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="42">
@@ -2884,30 +2852,30 @@
         <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Celebrating Ethel (IRE)</t>
+          <t>Love You More</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K42" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L42" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M42" t="n">
         <v>125.52</v>
       </c>
       <c r="N42" t="n">
-        <v>44.2</v>
+        <v>46.7</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2915,7 +2883,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2944,30 +2912,30 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Love You More</t>
+          <t>Celtic John (IRE)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K43" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L43" t="n">
-        <v>7.7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>125.52</v>
       </c>
       <c r="N43" t="n">
-        <v>49.2</v>
+        <v>43.9</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3004,30 +2972,30 @@
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Celtic John (IRE)</t>
+          <t>Letsbeatsepsis</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K44" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L44" t="n">
-        <v>8.449999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="M44" t="n">
         <v>125.52</v>
       </c>
       <c r="N44" t="n">
-        <v>43.9</v>
+        <v>35.2</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3064,30 +3032,30 @@
         <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Letsbeatsepsis</t>
+          <t>Fighting Poet (IRE)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L45" t="n">
-        <v>10.45</v>
+        <v>14.2</v>
       </c>
       <c r="M45" t="n">
         <v>125.52</v>
       </c>
       <c r="N45" t="n">
-        <v>41.4</v>
+        <v>34.7</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3123,40 +3091,24 @@
       <c r="F46" t="n">
         <v>6</v>
       </c>
-      <c r="G46" t="n">
-        <v>13</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fighting Poet (IRE)</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" t="n">
-        <v>130</v>
-      </c>
-      <c r="K46" t="n">
-        <v>50</v>
-      </c>
-      <c r="L46" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>125.52</v>
-      </c>
-      <c r="N46" t="n">
-        <v>34.7</v>
-      </c>
+          <t>Monks Mead</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3184,34 +3136,36 @@
         <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>A Lott Of Kane (IRE)</t>
+          <t>Cape Toronada (FR)</t>
         </is>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K47" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>75.90000000000001</v>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3240,28 +3194,30 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Cape Toronada (FR)</t>
+          <t>No Claims Bonus</t>
         </is>
       </c>
       <c r="I48" t="n">
         <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K48" t="n">
-        <v>53</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
       <c r="M48" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>75.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3269,7 +3225,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
@@ -3298,30 +3254,30 @@
         <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>No Claims Bonus</t>
+          <t>Lieutenant Sir</t>
         </is>
       </c>
       <c r="I49" t="n">
         <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K49" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>65.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3329,7 +3285,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3358,30 +3314,30 @@
         <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Lieutenant Sir</t>
+          <t>Rivera Queen (IRE)</t>
         </is>
       </c>
       <c r="I50" t="n">
         <v>3</v>
       </c>
       <c r="J50" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K50" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L50" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>70.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3389,7 +3345,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3418,30 +3374,30 @@
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Rivera Queen (IRE)</t>
+          <t>Poetic Grace (IRE)</t>
         </is>
       </c>
       <c r="I51" t="n">
         <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K51" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L51" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="M51" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>67.3</v>
+        <v>56.5</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3449,7 +3405,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3478,30 +3434,30 @@
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Poetic Grace (IRE)</t>
+          <t>Saeculamation (IRE)</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K52" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L52" t="n">
-        <v>4.9</v>
+        <v>8.15</v>
       </c>
       <c r="M52" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>56.5</v>
+        <v>45</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3509,7 +3465,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
@@ -3538,30 +3494,30 @@
         <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Saeculamation (IRE)</t>
+          <t>Arvana Belle (IRE)</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K53" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L53" t="n">
-        <v>8.15</v>
+        <v>9.65</v>
       </c>
       <c r="M53" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>48.9</v>
+        <v>46.1</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3569,7 +3525,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3597,40 +3553,24 @@
       <c r="F54" t="n">
         <v>6</v>
       </c>
-      <c r="G54" t="n">
-        <v>7</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Arvana Belle (IRE)</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" t="n">
-        <v>130</v>
-      </c>
-      <c r="K54" t="n">
-        <v>50</v>
-      </c>
-      <c r="L54" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="M54" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="N54" t="n">
-        <v>46.1</v>
-      </c>
+          <t>A Lott Of Kane (IRE)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3669,7 +3609,7 @@
         <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K55" t="n">
         <v>61</v>
@@ -3679,7 +3619,7 @@
         <v>61.92</v>
       </c>
       <c r="N55" t="n">
-        <v>72.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3687,7 +3627,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3787,7 +3727,7 @@
         <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K57" t="n">
         <v>69</v>
@@ -3799,7 +3739,7 @@
         <v>61.92</v>
       </c>
       <c r="N57" t="n">
-        <v>74.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3807,7 +3747,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
@@ -3927,7 +3867,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="60">
@@ -3967,7 +3907,7 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K60" t="n">
         <v>60</v>
@@ -3979,7 +3919,7 @@
         <v>61.92</v>
       </c>
       <c r="N60" t="n">
-        <v>58.4</v>
+        <v>53.5</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3987,7 +3927,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
@@ -4047,7 +3987,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -4087,10 +4027,10 @@
         <v>8</v>
       </c>
       <c r="J62" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K62" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L62" t="n">
         <v>4.7</v>
@@ -4099,7 +4039,7 @@
         <v>61.92</v>
       </c>
       <c r="N62" t="n">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4205,7 +4145,7 @@
         <v>9</v>
       </c>
       <c r="J64" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K64" t="n">
         <v>48</v>
@@ -4217,7 +4157,7 @@
         <v>76.11</v>
       </c>
       <c r="N64" t="n">
-        <v>45.3</v>
+        <v>37.5</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4225,7 +4165,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
@@ -4325,7 +4265,7 @@
         <v>7</v>
       </c>
       <c r="J66" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K66" t="n">
         <v>65</v>
@@ -4337,7 +4277,7 @@
         <v>76.11</v>
       </c>
       <c r="N66" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4345,7 +4285,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4385,7 +4325,7 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K67" t="n">
         <v>61</v>
@@ -4397,7 +4337,7 @@
         <v>76.11</v>
       </c>
       <c r="N67" t="n">
-        <v>15.2</v>
+        <v>8</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4445,7 +4385,7 @@
         <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K68" t="n">
         <v>60</v>
@@ -4457,7 +4397,7 @@
         <v>76.11</v>
       </c>
       <c r="N68" t="n">
-        <v>10.7</v>
+        <v>5.3</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4623,7 +4563,7 @@
         <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -4635,7 +4575,7 @@
         <v>64.65000000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>32.6</v>
+        <v>29.8</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4972,18 +4912,18 @@
         <v>4</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Ceinture Dorion</t>
+          <t>Turret (IRE)</t>
         </is>
       </c>
       <c r="I77" t="n">
         <v>3</v>
       </c>
       <c r="J77" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -4992,14 +4932,16 @@
       <c r="M77" t="n">
         <v>122.02</v>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>56.5</v>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5028,11 +4970,11 @@
         <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Turret (IRE)</t>
+          <t>Glory Road (GER)</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5044,12 +4986,14 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M78" t="n">
         <v>122.02</v>
       </c>
       <c r="N78" t="n">
-        <v>56.5</v>
+        <v>56.1</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5086,11 +5030,11 @@
         <v>4</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Glory Road (GER)</t>
+          <t>Steel Raven (IRE)</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -5103,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.15</v>
+        <v>3.9</v>
       </c>
       <c r="M79" t="n">
         <v>122.02</v>
       </c>
       <c r="N79" t="n">
-        <v>56.1</v>
+        <v>49</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5146,11 +5090,11 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Steel Raven (IRE)</t>
+          <t>Pepsea (IRE)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -5163,13 +5107,13 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="M80" t="n">
         <v>122.02</v>
       </c>
       <c r="N80" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5206,11 +5150,11 @@
         <v>4</v>
       </c>
       <c r="G81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Pepsea (IRE)</t>
+          <t>Affettuoso</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -5223,13 +5167,13 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="M81" t="n">
         <v>122.02</v>
       </c>
       <c r="N81" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5266,11 +5210,11 @@
         <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Affettuoso</t>
+          <t>Lorton Valley</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5283,13 +5227,13 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="M82" t="n">
         <v>122.02</v>
       </c>
       <c r="N82" t="n">
-        <v>48.4</v>
+        <v>42.3</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5326,11 +5270,11 @@
         <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Lorton Valley</t>
+          <t>Sun Lord (FR)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5343,13 +5287,13 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>6.5</v>
+        <v>8.25</v>
       </c>
       <c r="M83" t="n">
         <v>122.02</v>
       </c>
       <c r="N83" t="n">
-        <v>42.3</v>
+        <v>39.9</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5386,11 +5330,11 @@
         <v>4</v>
       </c>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sun Lord (FR)</t>
+          <t>Sanny Doo</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5400,20 +5344,20 @@
         <v>130</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L84" t="n">
-        <v>8.25</v>
+        <v>20.25</v>
       </c>
       <c r="M84" t="n">
         <v>122.02</v>
       </c>
       <c r="N84" t="n">
-        <v>39.9</v>
+        <v>32.7</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -5446,30 +5390,30 @@
         <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sanny Doo</t>
+          <t>Thistle Nil (IRE)</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K85" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>20.25</v>
+        <v>26.75</v>
       </c>
       <c r="M85" t="n">
         <v>122.02</v>
       </c>
       <c r="N85" t="n">
-        <v>32.7</v>
+        <v>27.5</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5506,11 +5450,11 @@
         <v>4</v>
       </c>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Thistle Nil (IRE)</t>
+          <t>Vintage Marsala</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5523,13 +5467,13 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>26.75</v>
+        <v>29.5</v>
       </c>
       <c r="M86" t="n">
         <v>122.02</v>
       </c>
       <c r="N86" t="n">
-        <v>30.4</v>
+        <v>27.3</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5566,30 +5510,30 @@
         <v>4</v>
       </c>
       <c r="G87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Vintage Marsala</t>
+          <t>Snake Hips</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>29.5</v>
+        <v>56.5</v>
       </c>
       <c r="M87" t="n">
         <v>122.02</v>
       </c>
       <c r="N87" t="n">
-        <v>27.3</v>
+        <v>-0</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5626,30 +5570,30 @@
         <v>4</v>
       </c>
       <c r="G88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Snake Hips</t>
+          <t>Sodeto</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>56.5</v>
+        <v>61.25</v>
       </c>
       <c r="M88" t="n">
         <v>122.02</v>
       </c>
       <c r="N88" t="n">
-        <v>-0</v>
+        <v>-3.3</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -5685,40 +5629,24 @@
       <c r="F89" t="n">
         <v>4</v>
       </c>
-      <c r="G89" t="n">
-        <v>12</v>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sodeto</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" t="n">
-        <v>142</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="M89" t="n">
-        <v>122.02</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-3.3</v>
-      </c>
+          <t>Ceinture Dorion</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5746,34 +5674,36 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Trilby</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K90" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
         <v>61.93</v>
       </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>78.8</v>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5802,28 +5732,30 @@
         <v>4</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Trilby</t>
+          <t>Parisiac (IRE)</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J91" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K91" t="n">
-        <v>80</v>
-      </c>
-      <c r="L91" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M91" t="n">
         <v>61.93</v>
       </c>
       <c r="N91" t="n">
-        <v>78.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5860,30 +5792,30 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Parisiac (IRE)</t>
+          <t>The Bell Conductor (IRE)</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J92" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K92" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L92" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
         <v>61.93</v>
       </c>
       <c r="N92" t="n">
-        <v>72.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -5891,7 +5823,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="93">
@@ -5920,30 +5852,30 @@
         <v>4</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>The Bell Conductor (IRE)</t>
+          <t>Station X</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K93" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L93" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M93" t="n">
         <v>61.93</v>
       </c>
       <c r="N93" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5951,7 +5883,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5980,30 +5912,30 @@
         <v>4</v>
       </c>
       <c r="G94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Station X</t>
+          <t>Franciscos Piece</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K94" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L94" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="M94" t="n">
         <v>61.93</v>
       </c>
       <c r="N94" t="n">
-        <v>68.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -6011,7 +5943,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6040,30 +5972,30 @@
         <v>4</v>
       </c>
       <c r="G95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Franciscos Piece</t>
+          <t>Vince Lamour (IRE)</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K95" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L95" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="M95" t="n">
         <v>61.93</v>
       </c>
       <c r="N95" t="n">
-        <v>64.40000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6100,15 +6032,15 @@
         <v>4</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Vince Lamour (IRE)</t>
+          <t>Hundred Caps</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
         <v>137</v>
@@ -6117,13 +6049,13 @@
         <v>79</v>
       </c>
       <c r="L96" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="M96" t="n">
         <v>61.93</v>
       </c>
       <c r="N96" t="n">
-        <v>54.7</v>
+        <v>54.4</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6160,30 +6092,30 @@
         <v>4</v>
       </c>
       <c r="G97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Hundred Caps</t>
+          <t>Spoof</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J97" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K97" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L97" t="n">
-        <v>6.1</v>
+        <v>6.13</v>
       </c>
       <c r="M97" t="n">
         <v>61.93</v>
       </c>
       <c r="N97" t="n">
-        <v>54.4</v>
+        <v>52.1</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6220,30 +6152,30 @@
         <v>4</v>
       </c>
       <c r="G98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Spoof</t>
+          <t>Arctic Summer</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K98" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L98" t="n">
-        <v>6.13</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="M98" t="n">
         <v>61.93</v>
       </c>
       <c r="N98" t="n">
-        <v>52.1</v>
+        <v>42.7</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6280,30 +6212,30 @@
         <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Arctic Summer</t>
+          <t>Qila</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K99" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L99" t="n">
-        <v>8.879999999999999</v>
+        <v>14.38</v>
       </c>
       <c r="M99" t="n">
         <v>61.93</v>
       </c>
       <c r="N99" t="n">
-        <v>42.7</v>
+        <v>16.3</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6311,7 +6243,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="100">
@@ -6340,38 +6272,38 @@
         <v>4</v>
       </c>
       <c r="G100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Qila</t>
+          <t>Peter The Wolf</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K100" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L100" t="n">
-        <v>14.38</v>
+        <v>21.38</v>
       </c>
       <c r="M100" t="n">
         <v>61.93</v>
       </c>
       <c r="N100" t="n">
-        <v>16.3</v>
+        <v>28</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -6399,40 +6331,24 @@
       <c r="F101" t="n">
         <v>4</v>
       </c>
-      <c r="G101" t="n">
-        <v>11</v>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Peter The Wolf</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" t="n">
-        <v>136</v>
-      </c>
-      <c r="K101" t="n">
-        <v>78</v>
-      </c>
-      <c r="L101" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="M101" t="n">
-        <v>61.93</v>
-      </c>
-      <c r="N101" t="n">
-        <v>28</v>
-      </c>
+          <t>Accrual</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P101" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6460,34 +6376,36 @@
         <v>5</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Golspie (IRE)</t>
+          <t>Jaminoz (IRE)</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J102" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K102" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
         <v>149.69</v>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>51.1</v>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-11.5</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="103">
@@ -6516,34 +6434,38 @@
         <v>5</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>V Twelve (IRE)</t>
+          <t>Naturalia</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K103" t="n">
-        <v>62</v>
-      </c>
-      <c r="L103" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M103" t="n">
         <v>149.69</v>
       </c>
-      <c r="N103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>51.1</v>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>-11.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="104">
@@ -6572,28 +6494,30 @@
         <v>5</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Jaminoz (IRE)</t>
+          <t>West Tyrone</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K104" t="n">
-        <v>60</v>
-      </c>
-      <c r="L104" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.85</v>
+      </c>
       <c r="M104" t="n">
         <v>149.69</v>
       </c>
       <c r="N104" t="n">
-        <v>55.6</v>
+        <v>57.7</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6601,7 +6525,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -6630,30 +6554,30 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Naturalia</t>
+          <t>Polygram</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K105" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L105" t="n">
-        <v>0.1</v>
+        <v>4.35</v>
       </c>
       <c r="M105" t="n">
         <v>149.69</v>
       </c>
       <c r="N105" t="n">
-        <v>56.1</v>
+        <v>54.8</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6661,7 +6585,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -6690,30 +6614,30 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>West Tyrone</t>
+          <t>Taylormade Lad (IRE)</t>
         </is>
       </c>
       <c r="I106" t="n">
         <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K106" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L106" t="n">
-        <v>0.85</v>
+        <v>4.85</v>
       </c>
       <c r="M106" t="n">
         <v>149.69</v>
       </c>
       <c r="N106" t="n">
-        <v>57.7</v>
+        <v>52</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6750,30 +6674,30 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Polygram</t>
+          <t>Dubai Venture (IRE)</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="K107" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="L107" t="n">
-        <v>4.35</v>
+        <v>5.6</v>
       </c>
       <c r="M107" t="n">
         <v>149.69</v>
       </c>
       <c r="N107" t="n">
-        <v>54.8</v>
+        <v>39.2</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -6781,7 +6705,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="108">
@@ -6810,30 +6734,30 @@
         <v>5</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Taylormade Lad (IRE)</t>
+          <t>Letmeseethecolts</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J108" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K108" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L108" t="n">
-        <v>4.85</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="M108" t="n">
         <v>149.69</v>
       </c>
       <c r="N108" t="n">
-        <v>52</v>
+        <v>41.2</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -6841,7 +6765,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -6870,30 +6794,30 @@
         <v>5</v>
       </c>
       <c r="G109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Dubai Venture (IRE)</t>
+          <t>Dr Rio (FR)</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J109" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K109" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="L109" t="n">
-        <v>5.6</v>
+        <v>10.2</v>
       </c>
       <c r="M109" t="n">
         <v>149.69</v>
       </c>
       <c r="N109" t="n">
-        <v>39.2</v>
+        <v>33.6</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6901,7 +6825,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6930,30 +6854,30 @@
         <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Letmeseethecolts</t>
+          <t>Junkyard Dog (IRE)</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K110" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="L110" t="n">
-        <v>5.7</v>
+        <v>19.2</v>
       </c>
       <c r="M110" t="n">
         <v>149.69</v>
       </c>
       <c r="N110" t="n">
-        <v>41.2</v>
+        <v>31</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -6961,7 +6885,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6990,34 +6914,34 @@
         <v>5</v>
       </c>
       <c r="G111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Dr Rio (FR)</t>
+          <t>Scotland The Brave</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J111" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K111" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L111" t="n">
-        <v>10.2</v>
+        <v>70.19999999999999</v>
       </c>
       <c r="M111" t="n">
         <v>149.69</v>
       </c>
       <c r="N111" t="n">
-        <v>36</v>
+        <v>18.3</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -7049,40 +6973,24 @@
       <c r="F112" t="n">
         <v>5</v>
       </c>
-      <c r="G112" t="n">
-        <v>9</v>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Junkyard Dog (IRE)</t>
-        </is>
-      </c>
-      <c r="I112" t="n">
-        <v>4</v>
-      </c>
-      <c r="J112" t="n">
-        <v>135</v>
-      </c>
-      <c r="K112" t="n">
-        <v>70</v>
-      </c>
-      <c r="L112" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M112" t="n">
-        <v>149.69</v>
-      </c>
-      <c r="N112" t="n">
-        <v>31</v>
-      </c>
+          <t>V Twelve (IRE)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7109,40 +7017,24 @@
       <c r="F113" t="n">
         <v>5</v>
       </c>
-      <c r="G113" t="n">
-        <v>10</v>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Scotland The Brave</t>
-        </is>
-      </c>
-      <c r="I113" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" t="n">
-        <v>135</v>
-      </c>
-      <c r="K113" t="n">
-        <v>70</v>
-      </c>
-      <c r="L113" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="M113" t="n">
-        <v>149.69</v>
-      </c>
-      <c r="N113" t="n">
-        <v>18.3</v>
-      </c>
+          <t>Golspie (IRE)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7170,34 +7062,36 @@
         <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Balmoral Boy (IRE)</t>
+          <t>Unchartedterritory (IRE)</t>
         </is>
       </c>
       <c r="I114" t="n">
         <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K114" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
         <v>120.91</v>
       </c>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>61.4</v>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>-11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -7226,34 +7120,38 @@
         <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Lightening Lad</t>
+          <t>Ephron (IRE)</t>
         </is>
       </c>
       <c r="I115" t="n">
         <v>3</v>
       </c>
       <c r="J115" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="K115" t="n">
-        <v>69</v>
-      </c>
-      <c r="L115" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M115" t="n">
         <v>120.91</v>
       </c>
-      <c r="N115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>53.2</v>
+      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>-11.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="116">
@@ -7282,28 +7180,30 @@
         <v>5</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Unchartedterritory (IRE)</t>
+          <t>Ibn Altheeb (IRE)</t>
         </is>
       </c>
       <c r="I116" t="n">
         <v>3</v>
       </c>
       <c r="J116" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K116" t="n">
-        <v>69</v>
-      </c>
-      <c r="L116" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="L116" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M116" t="n">
         <v>120.91</v>
       </c>
       <c r="N116" t="n">
-        <v>61.4</v>
+        <v>55.7</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -7311,7 +7211,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -7340,30 +7240,30 @@
         <v>5</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Ephron (IRE)</t>
+          <t>Attention Seeker (IRE)</t>
         </is>
       </c>
       <c r="I117" t="n">
         <v>3</v>
       </c>
       <c r="J117" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="K117" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="L117" t="n">
-        <v>1.5</v>
+        <v>3.65</v>
       </c>
       <c r="M117" t="n">
         <v>120.91</v>
       </c>
       <c r="N117" t="n">
-        <v>57.5</v>
+        <v>47.7</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -7371,7 +7271,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="118">
@@ -7400,30 +7300,30 @@
         <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Ibn Altheeb (IRE)</t>
+          <t>Mr Moonshine (IRE)</t>
         </is>
       </c>
       <c r="I118" t="n">
         <v>3</v>
       </c>
       <c r="J118" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K118" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L118" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="M118" t="n">
         <v>120.91</v>
       </c>
       <c r="N118" t="n">
-        <v>55.7</v>
+        <v>50.9</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -7431,7 +7331,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -7460,30 +7360,30 @@
         <v>5</v>
       </c>
       <c r="G119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Attention Seeker (IRE)</t>
+          <t>Clocker</t>
         </is>
       </c>
       <c r="I119" t="n">
         <v>3</v>
       </c>
       <c r="J119" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K119" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L119" t="n">
-        <v>3.65</v>
+        <v>5.430000000000001</v>
       </c>
       <c r="M119" t="n">
         <v>120.91</v>
       </c>
       <c r="N119" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -7491,7 +7391,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -7520,30 +7420,30 @@
         <v>5</v>
       </c>
       <c r="G120" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Mr Moonshine (IRE)</t>
+          <t>Hatamoto</t>
         </is>
       </c>
       <c r="I120" t="n">
         <v>3</v>
       </c>
       <c r="J120" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K120" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L120" t="n">
-        <v>5.4</v>
+        <v>13.43</v>
       </c>
       <c r="M120" t="n">
         <v>120.91</v>
       </c>
       <c r="N120" t="n">
-        <v>50.9</v>
+        <v>25.9</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -7551,7 +7451,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="121">
@@ -7580,30 +7480,30 @@
         <v>5</v>
       </c>
       <c r="G121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Clocker</t>
+          <t>Cosmic Man (IRE)</t>
         </is>
       </c>
       <c r="I121" t="n">
         <v>3</v>
       </c>
       <c r="J121" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K121" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L121" t="n">
-        <v>5.43</v>
+        <v>15.93</v>
       </c>
       <c r="M121" t="n">
         <v>120.91</v>
       </c>
       <c r="N121" t="n">
-        <v>48.1</v>
+        <v>28.2</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -7611,7 +7511,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7640,38 +7540,38 @@
         <v>5</v>
       </c>
       <c r="G122" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Hatamoto</t>
+          <t>Espanita (IRE)</t>
         </is>
       </c>
       <c r="I122" t="n">
         <v>3</v>
       </c>
       <c r="J122" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="K122" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="L122" t="n">
-        <v>13.43</v>
+        <v>26.93</v>
       </c>
       <c r="M122" t="n">
         <v>120.91</v>
       </c>
       <c r="N122" t="n">
-        <v>25.9</v>
+        <v>33.8</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -7700,34 +7600,34 @@
         <v>5</v>
       </c>
       <c r="G123" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Cosmic Man (IRE)</t>
+          <t>Scheffler (IRE)</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>3</v>
       </c>
       <c r="J123" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K123" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L123" t="n">
-        <v>15.93</v>
+        <v>54.93</v>
       </c>
       <c r="M123" t="n">
         <v>120.91</v>
       </c>
       <c r="N123" t="n">
-        <v>28.2</v>
+        <v>13.6</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -7759,40 +7659,24 @@
       <c r="F124" t="n">
         <v>5</v>
       </c>
-      <c r="G124" t="n">
-        <v>9</v>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Espanita (IRE)</t>
-        </is>
-      </c>
-      <c r="I124" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" t="n">
-        <v>132</v>
-      </c>
-      <c r="K124" t="n">
-        <v>67</v>
-      </c>
-      <c r="L124" t="n">
-        <v>26.93</v>
-      </c>
-      <c r="M124" t="n">
-        <v>120.91</v>
-      </c>
-      <c r="N124" t="n">
-        <v>33.8</v>
-      </c>
+          <t>Lightening Lad</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P124" t="n">
-        <v>2</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7819,40 +7703,24 @@
       <c r="F125" t="n">
         <v>5</v>
       </c>
-      <c r="G125" t="n">
-        <v>10</v>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Scheffler (IRE)</t>
-        </is>
-      </c>
-      <c r="I125" t="n">
-        <v>3</v>
-      </c>
-      <c r="J125" t="n">
-        <v>135</v>
-      </c>
-      <c r="K125" t="n">
-        <v>70</v>
-      </c>
-      <c r="L125" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="M125" t="n">
-        <v>120.91</v>
-      </c>
-      <c r="N125" t="n">
-        <v>13.6</v>
-      </c>
+          <t>Balmoral Boy (IRE)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7880,11 +7748,11 @@
         <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Minzazi (IRE)</t>
+          <t>Undiscovered (IRE)</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -7900,14 +7768,16 @@
       <c r="M126" t="n">
         <v>79.15000000000001</v>
       </c>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>68.2</v>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7936,28 +7806,30 @@
         <v>5</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Undiscovered (IRE)</t>
+          <t>Green Titan</t>
         </is>
       </c>
       <c r="I127" t="n">
         <v>2</v>
       </c>
       <c r="J127" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
       </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>2</v>
+      </c>
       <c r="M127" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N127" t="n">
-        <v>68.2</v>
+        <v>61.1</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -7994,11 +7866,11 @@
         <v>5</v>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Green Titan</t>
+          <t>Lord Of Winterfell</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -8011,13 +7883,13 @@
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M128" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N128" t="n">
-        <v>61.1</v>
+        <v>58.7</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -8054,30 +7926,30 @@
         <v>5</v>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Lord Of Winterfell</t>
+          <t>Empire Rising (IRE)</t>
         </is>
       </c>
       <c r="I129" t="n">
         <v>2</v>
       </c>
       <c r="J129" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="M129" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N129" t="n">
-        <v>58.7</v>
+        <v>57.8</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -8114,11 +7986,11 @@
         <v>5</v>
       </c>
       <c r="G130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Empire Rising (IRE)</t>
+          <t>Foscarini (IRE)</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -8131,13 +8003,13 @@
         <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M130" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N130" t="n">
-        <v>57.8</v>
+        <v>50.9</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -8174,11 +8046,11 @@
         <v>5</v>
       </c>
       <c r="G131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Foscarini (IRE)</t>
+          <t>Secret Society (IRE)</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -8191,13 +8063,13 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="M131" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N131" t="n">
-        <v>50.9</v>
+        <v>49</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8234,30 +8106,30 @@
         <v>5</v>
       </c>
       <c r="G132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Secret Society (IRE)</t>
+          <t>Ten Year Stretch (IRE)</t>
         </is>
       </c>
       <c r="I132" t="n">
         <v>2</v>
       </c>
       <c r="J132" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>5.55</v>
+        <v>6.8</v>
       </c>
       <c r="M132" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N132" t="n">
-        <v>49</v>
+        <v>43.2</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -8294,11 +8166,11 @@
         <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Ten Year Stretch (IRE)</t>
+          <t>Benefacta (IRE)</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -8311,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>6.8</v>
+        <v>7.55</v>
       </c>
       <c r="M133" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N133" t="n">
-        <v>43.2</v>
+        <v>40.1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -8354,30 +8226,30 @@
         <v>5</v>
       </c>
       <c r="G134" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Benefacta (IRE)</t>
+          <t>Half A Hoof (IRE)</t>
         </is>
       </c>
       <c r="I134" t="n">
         <v>2</v>
       </c>
       <c r="J134" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>7.55</v>
+        <v>10.8</v>
       </c>
       <c r="M134" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N134" t="n">
-        <v>40.1</v>
+        <v>25.1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -8414,30 +8286,30 @@
         <v>5</v>
       </c>
       <c r="G135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Half A Hoof (IRE)</t>
+          <t>Prince Kameo</t>
         </is>
       </c>
       <c r="I135" t="n">
         <v>2</v>
       </c>
       <c r="J135" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>10.8</v>
+        <v>14.3</v>
       </c>
       <c r="M135" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N135" t="n">
-        <v>25.1</v>
+        <v>22.5</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -8474,30 +8346,30 @@
         <v>5</v>
       </c>
       <c r="G136" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Prince Kameo</t>
+          <t>Glory Bound (IRE)</t>
         </is>
       </c>
       <c r="I136" t="n">
         <v>2</v>
       </c>
       <c r="J136" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>14.3</v>
+        <v>16.8</v>
       </c>
       <c r="M136" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="N136" t="n">
-        <v>22.5</v>
+        <v>6.1</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -8533,40 +8405,24 @@
       <c r="F137" t="n">
         <v>5</v>
       </c>
-      <c r="G137" t="n">
-        <v>11</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Glory Bound (IRE)</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>2</v>
-      </c>
-      <c r="J137" t="n">
-        <v>127</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M137" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="N137" t="n">
-        <v>6.1</v>
-      </c>
+          <t>Minzazi (IRE)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8594,18 +8450,18 @@
         <v>5</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Rattenbury (IRE)</t>
+          <t>Flying Pirate (IRE)</t>
         </is>
       </c>
       <c r="I138" t="n">
         <v>2</v>
       </c>
       <c r="J138" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -8614,14 +8470,16 @@
       <c r="M138" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="n">
+        <v>79.40000000000001</v>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P138" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8650,11 +8508,11 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Flying Pirate (IRE)</t>
+          <t>Harry Knows (IRE)</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -8666,12 +8524,14 @@
       <c r="K139" t="n">
         <v>0</v>
       </c>
-      <c r="L139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M139" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N139" t="n">
-        <v>79.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -8708,30 +8568,30 @@
         <v>5</v>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Harry Knows (IRE)</t>
+          <t>Aphra Behn</t>
         </is>
       </c>
       <c r="I140" t="n">
         <v>2</v>
       </c>
       <c r="J140" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0.1</v>
+        <v>1.85</v>
       </c>
       <c r="M140" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N140" t="n">
-        <v>77.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -8768,30 +8628,30 @@
         <v>5</v>
       </c>
       <c r="G141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Aphra Behn</t>
+          <t>Invicta Rose (IRE)</t>
         </is>
       </c>
       <c r="I141" t="n">
         <v>2</v>
       </c>
       <c r="J141" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>1.85</v>
+        <v>7.85</v>
       </c>
       <c r="M141" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N141" t="n">
-        <v>64.5</v>
+        <v>53.4</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -8799,7 +8659,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="142">
@@ -8828,30 +8688,30 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Invicta Rose (IRE)</t>
+          <t>No More Pino (IRE)</t>
         </is>
       </c>
       <c r="I142" t="n">
         <v>2</v>
       </c>
       <c r="J142" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>7.85</v>
+        <v>8.35</v>
       </c>
       <c r="M142" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N142" t="n">
-        <v>53.4</v>
+        <v>56.7</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -8859,7 +8719,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -8888,30 +8748,30 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>No More Pino (IRE)</t>
+          <t>Beresford Gap (IRE)</t>
         </is>
       </c>
       <c r="I143" t="n">
         <v>2</v>
       </c>
       <c r="J143" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>8.35</v>
+        <v>8.5</v>
       </c>
       <c r="M143" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N143" t="n">
-        <v>56.7</v>
+        <v>53.8</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -8948,30 +8808,30 @@
         <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Beresford Gap (IRE)</t>
+          <t>Walbrook (IRE)</t>
         </is>
       </c>
       <c r="I144" t="n">
         <v>2</v>
       </c>
       <c r="J144" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="M144" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N144" t="n">
-        <v>53.8</v>
+        <v>52.3</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -8979,7 +8839,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -9008,11 +8868,11 @@
         <v>5</v>
       </c>
       <c r="G145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Walbrook (IRE)</t>
+          <t>Green Dividend</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -9025,13 +8885,13 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>9.5</v>
+        <v>9.65</v>
       </c>
       <c r="M145" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N145" t="n">
-        <v>52.3</v>
+        <v>50.8</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -9068,11 +8928,11 @@
         <v>5</v>
       </c>
       <c r="G146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Green Dividend</t>
+          <t>Goodwood Meteor</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -9085,13 +8945,13 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>9.65</v>
+        <v>12.4</v>
       </c>
       <c r="M146" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N146" t="n">
-        <v>50.8</v>
+        <v>40.3</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9128,11 +8988,11 @@
         <v>5</v>
       </c>
       <c r="G147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Goodwood Meteor</t>
+          <t>Blue Skies Above</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -9145,13 +9005,13 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>12.4</v>
+        <v>13.15</v>
       </c>
       <c r="M147" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N147" t="n">
-        <v>40.3</v>
+        <v>38</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9188,34 +9048,34 @@
         <v>5</v>
       </c>
       <c r="G148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Blue Skies Above</t>
+          <t>Make No Mistake</t>
         </is>
       </c>
       <c r="I148" t="n">
         <v>2</v>
       </c>
       <c r="J148" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>13.15</v>
+        <v>22.65</v>
       </c>
       <c r="M148" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="N148" t="n">
-        <v>38</v>
+        <v>34.4</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -9247,40 +9107,24 @@
       <c r="F149" t="n">
         <v>5</v>
       </c>
-      <c r="G149" t="n">
-        <v>11</v>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Make No Mistake</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" t="n">
-        <v>130</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="M149" t="n">
-        <v>77.81999999999999</v>
-      </c>
-      <c r="N149" t="n">
-        <v>34.4</v>
-      </c>
+          <t>Rattenbury (IRE)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9308,34 +9152,36 @@
         <v>5</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Lodge (IRE)</t>
+          <t>Supreme King (IRE)</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J150" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K150" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
         <v>77.18000000000001</v>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="n">
+        <v>80.09999999999999</v>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -9364,28 +9210,30 @@
         <v>5</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Supreme King (IRE)</t>
+          <t>Arantes Nascimento</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J151" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K151" t="n">
-        <v>75</v>
-      </c>
-      <c r="L151" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M151" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N151" t="n">
-        <v>80.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -9422,30 +9270,30 @@
         <v>5</v>
       </c>
       <c r="G152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Arantes Nascimento</t>
+          <t>Distant Rumble</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J152" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K152" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L152" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="M152" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N152" t="n">
-        <v>78.2</v>
+        <v>73.2</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -9482,30 +9330,30 @@
         <v>5</v>
       </c>
       <c r="G153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Distant Rumble</t>
+          <t>Lazzar (IRE)</t>
         </is>
       </c>
       <c r="I153" t="n">
         <v>4</v>
       </c>
       <c r="J153" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K153" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L153" t="n">
-        <v>0.65</v>
+        <v>3.4</v>
       </c>
       <c r="M153" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N153" t="n">
-        <v>73.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -9542,30 +9390,30 @@
         <v>5</v>
       </c>
       <c r="G154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Lazzar (IRE)</t>
+          <t>Invincible Speed (IRE)</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J154" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K154" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L154" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="M154" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N154" t="n">
-        <v>67.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9602,30 +9450,30 @@
         <v>5</v>
       </c>
       <c r="G155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Invincible Speed (IRE)</t>
+          <t>Thunderous Love</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>5</v>
       </c>
       <c r="J155" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K155" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L155" t="n">
-        <v>4.4</v>
+        <v>8.65</v>
       </c>
       <c r="M155" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N155" t="n">
-        <v>64.3</v>
+        <v>49.9</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -9662,30 +9510,30 @@
         <v>5</v>
       </c>
       <c r="G156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Thunderous Love</t>
+          <t>Addictive (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J156" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K156" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L156" t="n">
-        <v>8.65</v>
+        <v>9.65</v>
       </c>
       <c r="M156" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N156" t="n">
-        <v>49.9</v>
+        <v>41.4</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9722,30 +9570,30 @@
         <v>5</v>
       </c>
       <c r="G157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Addictive (IRE)</t>
+          <t>Phoenix Moon (IRE)</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J157" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K157" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L157" t="n">
-        <v>9.65</v>
+        <v>10.15</v>
       </c>
       <c r="M157" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N157" t="n">
-        <v>41.4</v>
+        <v>37.3</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9782,30 +9630,30 @@
         <v>5</v>
       </c>
       <c r="G158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Phoenix Moon (IRE)</t>
+          <t>Unico</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>5</v>
       </c>
       <c r="J158" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="K158" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="L158" t="n">
-        <v>10.15</v>
+        <v>12.15</v>
       </c>
       <c r="M158" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N158" t="n">
-        <v>37.3</v>
+        <v>27.4</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9842,30 +9690,30 @@
         <v>5</v>
       </c>
       <c r="G159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Unico</t>
+          <t>Newsreader (IRE)</t>
         </is>
       </c>
       <c r="I159" t="n">
         <v>5</v>
       </c>
       <c r="J159" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="K159" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="L159" t="n">
-        <v>12.15</v>
+        <v>19.15</v>
       </c>
       <c r="M159" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="N159" t="n">
-        <v>27.4</v>
+        <v>25.1</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -9901,40 +9749,24 @@
       <c r="F160" t="n">
         <v>5</v>
       </c>
-      <c r="G160" t="n">
-        <v>10</v>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Newsreader (IRE)</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>5</v>
-      </c>
-      <c r="J160" t="n">
-        <v>133</v>
-      </c>
-      <c r="K160" t="n">
-        <v>73</v>
-      </c>
-      <c r="L160" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="M160" t="n">
-        <v>77.18000000000001</v>
-      </c>
-      <c r="N160" t="n">
-        <v>25.1</v>
-      </c>
+          <t>Lodge (IRE)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9962,11 +9794,11 @@
         <v>4</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Rajiba</t>
+          <t>Lucky Luna (IRE)</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -9982,14 +9814,16 @@
       <c r="M161" t="n">
         <v>92.79000000000001</v>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>62.8</v>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -10018,11 +9852,11 @@
         <v>4</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Lucky Luna (IRE)</t>
+          <t>Siddal</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -10034,12 +9868,14 @@
       <c r="K162" t="n">
         <v>0</v>
       </c>
-      <c r="L162" t="inlineStr"/>
+      <c r="L162" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M162" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N162" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -10076,11 +9912,11 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Siddal</t>
+          <t>Sapphire Secret</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -10093,13 +9929,13 @@
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M163" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N163" t="n">
-        <v>61.8</v>
+        <v>60.7</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -10136,30 +9972,30 @@
         <v>4</v>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sapphire Secret</t>
+          <t>Bold Shout (IRE)</t>
         </is>
       </c>
       <c r="I164" t="n">
         <v>3</v>
       </c>
       <c r="J164" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0.6</v>
+        <v>4.35</v>
       </c>
       <c r="M164" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N164" t="n">
-        <v>60.7</v>
+        <v>57.4</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -10196,30 +10032,30 @@
         <v>4</v>
       </c>
       <c r="G165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bold Shout (IRE)</t>
+          <t>Areti</t>
         </is>
       </c>
       <c r="I165" t="n">
         <v>3</v>
       </c>
       <c r="J165" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L165" t="n">
-        <v>4.35</v>
+        <v>7.1</v>
       </c>
       <c r="M165" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N165" t="n">
-        <v>57.4</v>
+        <v>44.8</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10227,7 +10063,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="166">
@@ -10256,30 +10092,30 @@
         <v>4</v>
       </c>
       <c r="G166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Areti</t>
+          <t>Back At One (IRE)</t>
         </is>
       </c>
       <c r="I166" t="n">
         <v>3</v>
       </c>
       <c r="J166" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K166" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>7.1</v>
+        <v>7.85</v>
       </c>
       <c r="M166" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N166" t="n">
-        <v>44.8</v>
+        <v>46.8</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10287,7 +10123,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -10316,11 +10152,11 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Back At One (IRE)</t>
+          <t>Cosmic Jive (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -10333,13 +10169,13 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>7.85</v>
+        <v>8</v>
       </c>
       <c r="M167" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N167" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -10376,30 +10212,30 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Cosmic Jive (IRE)</t>
+          <t>Bright Summer (IRE)</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>3</v>
       </c>
       <c r="J168" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L168" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="M168" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N168" t="n">
-        <v>45.8</v>
+        <v>44.9</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -10436,30 +10272,30 @@
         <v>4</v>
       </c>
       <c r="G169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Bright Summer (IRE)</t>
+          <t>Hugh</t>
         </is>
       </c>
       <c r="I169" t="n">
         <v>3</v>
       </c>
       <c r="J169" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K169" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="M169" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N169" t="n">
-        <v>44.9</v>
+        <v>41.3</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -10467,7 +10303,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -10496,11 +10332,11 @@
         <v>4</v>
       </c>
       <c r="G170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Hugh</t>
+          <t>Le Samourai (IRE)</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -10513,13 +10349,13 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M170" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N170" t="n">
-        <v>41.3</v>
+        <v>29.5</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -10556,30 +10392,30 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Le Samourai (IRE)</t>
+          <t>Paint Your Palette (USA)</t>
         </is>
       </c>
       <c r="I171" t="n">
         <v>3</v>
       </c>
       <c r="J171" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="M171" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N171" t="n">
-        <v>29.5</v>
+        <v>8.9</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -10587,7 +10423,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="172">
@@ -10616,38 +10452,38 @@
         <v>4</v>
       </c>
       <c r="G172" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Paint Your Palette (USA)</t>
+          <t>Jeans Boy (IRE)</t>
         </is>
       </c>
       <c r="I172" t="n">
         <v>3</v>
       </c>
       <c r="J172" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
       <c r="M172" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N172" t="n">
-        <v>8.9</v>
+        <v>28</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -10676,30 +10512,30 @@
         <v>4</v>
       </c>
       <c r="G173" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Jeans Boy (IRE)</t>
+          <t>Dupont Circle (IRE)</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J173" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>25.5</v>
+        <v>42.5</v>
       </c>
       <c r="M173" t="n">
         <v>92.79000000000001</v>
       </c>
       <c r="N173" t="n">
-        <v>28</v>
+        <v>7.5</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10707,7 +10543,7 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -10735,40 +10571,24 @@
       <c r="F174" t="n">
         <v>4</v>
       </c>
-      <c r="G174" t="n">
-        <v>13</v>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Dupont Circle (IRE)</t>
-        </is>
-      </c>
-      <c r="I174" t="n">
-        <v>4</v>
-      </c>
-      <c r="J174" t="n">
-        <v>140</v>
-      </c>
-      <c r="K174" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M174" t="n">
-        <v>92.79000000000001</v>
-      </c>
-      <c r="N174" t="n">
-        <v>7.5</v>
-      </c>
+          <t>Rajiba</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10796,11 +10616,11 @@
         <v>3</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Herstmonceux</t>
+          <t>Besieged</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -10816,14 +10636,16 @@
       <c r="M175" t="n">
         <v>133.96</v>
       </c>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="n">
+        <v>78.5</v>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -10852,11 +10674,11 @@
         <v>3</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Besieged</t>
+          <t>Easwrith Destiny</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -10868,12 +10690,14 @@
       <c r="K176" t="n">
         <v>0</v>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="n">
+        <v>14</v>
+      </c>
       <c r="M176" t="n">
         <v>133.96</v>
       </c>
       <c r="N176" t="n">
-        <v>78.5</v>
+        <v>54</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -10881,7 +10705,7 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="177">
@@ -10910,30 +10734,30 @@
         <v>3</v>
       </c>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Easwrith Destiny</t>
+          <t>Poor Relation (FR)</t>
         </is>
       </c>
       <c r="I177" t="n">
         <v>3</v>
       </c>
       <c r="J177" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M177" t="n">
         <v>133.96</v>
       </c>
       <c r="N177" t="n">
-        <v>54</v>
+        <v>41.4</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -10941,7 +10765,7 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="178">
@@ -10970,30 +10794,30 @@
         <v>3</v>
       </c>
       <c r="G178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Poor Relation (FR)</t>
+          <t>Much</t>
         </is>
       </c>
       <c r="I178" t="n">
         <v>3</v>
       </c>
       <c r="J178" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>17</v>
+        <v>18.75</v>
       </c>
       <c r="M178" t="n">
         <v>133.96</v>
       </c>
       <c r="N178" t="n">
-        <v>41.4</v>
+        <v>44.5</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -11001,7 +10825,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="179">
@@ -11030,11 +10854,11 @@
         <v>3</v>
       </c>
       <c r="G179" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Much</t>
+          <t>Last Trump</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -11047,21 +10871,21 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>18.75</v>
+        <v>20.75</v>
       </c>
       <c r="M179" t="n">
         <v>133.96</v>
       </c>
       <c r="N179" t="n">
-        <v>44.5</v>
+        <v>56.5</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -11090,11 +10914,11 @@
         <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Last Trump</t>
+          <t>Notable Charm</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -11107,13 +10931,13 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>20.75</v>
+        <v>24.25</v>
       </c>
       <c r="M180" t="n">
         <v>133.96</v>
       </c>
       <c r="N180" t="n">
-        <v>56.5</v>
+        <v>51.5</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -11121,7 +10945,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -11150,11 +10974,11 @@
         <v>3</v>
       </c>
       <c r="G181" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Notable Charm</t>
+          <t>Long Reign</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -11167,13 +10991,13 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>24.25</v>
+        <v>26.75</v>
       </c>
       <c r="M181" t="n">
         <v>133.96</v>
       </c>
       <c r="N181" t="n">
-        <v>51.5</v>
+        <v>49.7</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -11210,11 +11034,11 @@
         <v>3</v>
       </c>
       <c r="G182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Long Reign</t>
+          <t>Centrum</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -11227,13 +11051,13 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>26.75</v>
+        <v>27.5</v>
       </c>
       <c r="M182" t="n">
         <v>133.96</v>
       </c>
       <c r="N182" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -11270,11 +11094,11 @@
         <v>3</v>
       </c>
       <c r="G183" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Centrum</t>
+          <t>Traveling Man</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -11287,13 +11111,13 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>27.5</v>
+        <v>36.5</v>
       </c>
       <c r="M183" t="n">
         <v>133.96</v>
       </c>
       <c r="N183" t="n">
-        <v>49</v>
+        <v>45.2</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -11330,11 +11154,11 @@
         <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Traveling Man</t>
+          <t>Cartrefle</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -11347,13 +11171,13 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>36.5</v>
+        <v>42.5</v>
       </c>
       <c r="M184" t="n">
         <v>133.96</v>
       </c>
       <c r="N184" t="n">
-        <v>45.2</v>
+        <v>42.5</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -11361,7 +11185,7 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -11389,40 +11213,24 @@
       <c r="F185" t="n">
         <v>3</v>
       </c>
-      <c r="G185" t="n">
-        <v>10</v>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Cartrefle</t>
-        </is>
-      </c>
-      <c r="I185" t="n">
-        <v>3</v>
-      </c>
-      <c r="J185" t="n">
-        <v>133</v>
-      </c>
-      <c r="K185" t="n">
-        <v>0</v>
-      </c>
-      <c r="L185" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M185" t="n">
-        <v>133.96</v>
-      </c>
-      <c r="N185" t="n">
-        <v>42.5</v>
-      </c>
+          <t>Herstmonceux</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P185" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11450,34 +11258,36 @@
         <v>4</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Typical Woman</t>
+          <t>Regal Charm (IRE)</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J186" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="K186" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="n">
         <v>134.18</v>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="n">
+        <v>79.2</v>
+      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -11506,28 +11316,30 @@
         <v>4</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Regal Charm (IRE)</t>
+          <t>Royal Poetry (IRE)</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J187" t="n">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="K187" t="n">
-        <v>81</v>
-      </c>
-      <c r="L187" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="L187" t="n">
+        <v>6.5</v>
+      </c>
       <c r="M187" t="n">
         <v>134.18</v>
       </c>
       <c r="N187" t="n">
-        <v>79.2</v>
+        <v>58.3</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -11564,11 +11376,11 @@
         <v>4</v>
       </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Royal Poetry (IRE)</t>
+          <t>Affection (FR)</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -11578,16 +11390,16 @@
         <v>126</v>
       </c>
       <c r="K188" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L188" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="M188" t="n">
         <v>134.18</v>
       </c>
       <c r="N188" t="n">
-        <v>58.3</v>
+        <v>56.8</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -11595,7 +11407,7 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -11624,30 +11436,30 @@
         <v>4</v>
       </c>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Affection (FR)</t>
+          <t>Albus Anne</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J189" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K189" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="L189" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M189" t="n">
         <v>134.18</v>
       </c>
       <c r="N189" t="n">
-        <v>60.1</v>
+        <v>49.8</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -11655,7 +11467,7 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="190">
@@ -11684,15 +11496,15 @@
         <v>4</v>
       </c>
       <c r="G190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Albus Anne</t>
+          <t>Jazzy Baby</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J190" t="n">
         <v>132</v>
@@ -11701,13 +11513,13 @@
         <v>70</v>
       </c>
       <c r="L190" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M190" t="n">
         <v>134.18</v>
       </c>
       <c r="N190" t="n">
-        <v>49.8</v>
+        <v>38.5</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -11744,30 +11556,30 @@
         <v>4</v>
       </c>
       <c r="G191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Jazzy Baby</t>
+          <t>Rossa Raheen</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J191" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="K191" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L191" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M191" t="n">
         <v>134.18</v>
       </c>
       <c r="N191" t="n">
-        <v>38.5</v>
+        <v>29.2</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -11804,38 +11616,38 @@
         <v>4</v>
       </c>
       <c r="G192" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Rossa Raheen</t>
+          <t>Morven (IRE)</t>
         </is>
       </c>
       <c r="I192" t="n">
         <v>3</v>
       </c>
       <c r="J192" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="K192" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L192" t="n">
-        <v>20</v>
+        <v>20.15</v>
       </c>
       <c r="M192" t="n">
         <v>134.18</v>
       </c>
       <c r="N192" t="n">
-        <v>29.2</v>
+        <v>52.2</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -11863,40 +11675,24 @@
       <c r="F193" t="n">
         <v>4</v>
       </c>
-      <c r="G193" t="n">
-        <v>7</v>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Morven (IRE)</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
-        <v>3</v>
-      </c>
-      <c r="J193" t="n">
-        <v>131</v>
-      </c>
-      <c r="K193" t="n">
-        <v>82</v>
-      </c>
-      <c r="L193" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="M193" t="n">
-        <v>134.18</v>
-      </c>
-      <c r="N193" t="n">
-        <v>52.2</v>
-      </c>
+          <t>Typical Woman</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P193" t="n">
-        <v>3</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11924,34 +11720,36 @@
         <v>6</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Thats Random</t>
+          <t>Maid In Devon</t>
         </is>
       </c>
       <c r="I194" t="n">
         <v>3</v>
       </c>
       <c r="J194" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K194" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
         <v>77.83</v>
       </c>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" t="n">
+        <v>71.3</v>
+      </c>
       <c r="O194" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -11980,28 +11778,30 @@
         <v>6</v>
       </c>
       <c r="G195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Maid In Devon</t>
+          <t>Madman</t>
         </is>
       </c>
       <c r="I195" t="n">
         <v>3</v>
       </c>
       <c r="J195" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K195" t="n">
-        <v>57</v>
-      </c>
-      <c r="L195" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="L195" t="n">
+        <v>3.25</v>
+      </c>
       <c r="M195" t="n">
         <v>77.83</v>
       </c>
       <c r="N195" t="n">
-        <v>71.3</v>
+        <v>65.2</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -12038,11 +11838,11 @@
         <v>6</v>
       </c>
       <c r="G196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Madman</t>
+          <t>Stock Market</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -12055,13 +11855,13 @@
         <v>59</v>
       </c>
       <c r="L196" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="M196" t="n">
         <v>77.83</v>
       </c>
       <c r="N196" t="n">
-        <v>65.2</v>
+        <v>63.4</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -12098,30 +11898,30 @@
         <v>6</v>
       </c>
       <c r="G197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Stock Market</t>
+          <t>Wayward Queen</t>
         </is>
       </c>
       <c r="I197" t="n">
         <v>3</v>
       </c>
       <c r="J197" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K197" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L197" t="n">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="M197" t="n">
         <v>77.83</v>
       </c>
       <c r="N197" t="n">
-        <v>63.4</v>
+        <v>48.8</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -12129,7 +11929,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="198">
@@ -12158,30 +11958,30 @@
         <v>6</v>
       </c>
       <c r="G198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Wayward Queen</t>
+          <t>Tenzi (IRE)</t>
         </is>
       </c>
       <c r="I198" t="n">
         <v>3</v>
       </c>
       <c r="J198" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K198" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="L198" t="n">
-        <v>5.15</v>
+        <v>7.4</v>
       </c>
       <c r="M198" t="n">
         <v>77.83</v>
       </c>
       <c r="N198" t="n">
-        <v>48.8</v>
+        <v>56.3</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -12189,7 +11989,7 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -12218,30 +12018,30 @@
         <v>6</v>
       </c>
       <c r="G199" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Tenzi (IRE)</t>
+          <t>Follow My Heart</t>
         </is>
       </c>
       <c r="I199" t="n">
         <v>3</v>
       </c>
       <c r="J199" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="K199" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="L199" t="n">
-        <v>7.4</v>
+        <v>8.15</v>
       </c>
       <c r="M199" t="n">
         <v>77.83</v>
       </c>
       <c r="N199" t="n">
-        <v>56.3</v>
+        <v>41.3</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -12249,7 +12049,7 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -12278,30 +12078,30 @@
         <v>6</v>
       </c>
       <c r="G200" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Follow My Heart</t>
+          <t>Yes Waliim (IRE)</t>
         </is>
       </c>
       <c r="I200" t="n">
         <v>3</v>
       </c>
       <c r="J200" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="K200" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="L200" t="n">
-        <v>8.15</v>
+        <v>11.15</v>
       </c>
       <c r="M200" t="n">
         <v>77.83</v>
       </c>
       <c r="N200" t="n">
-        <v>41.3</v>
+        <v>35.3</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -12309,7 +12109,7 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="201">
@@ -12338,30 +12138,30 @@
         <v>6</v>
       </c>
       <c r="G201" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Yes Waliim (IRE)</t>
+          <t>Grimeses Special (IRE)</t>
         </is>
       </c>
       <c r="I201" t="n">
         <v>3</v>
       </c>
       <c r="J201" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K201" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L201" t="n">
-        <v>11.15</v>
+        <v>12.9</v>
       </c>
       <c r="M201" t="n">
         <v>77.83</v>
       </c>
       <c r="N201" t="n">
-        <v>42.7</v>
+        <v>38.4</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -12398,30 +12198,30 @@
         <v>6</v>
       </c>
       <c r="G202" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Grimeses Special (IRE)</t>
+          <t>Marra Donna (IRE)</t>
         </is>
       </c>
       <c r="I202" t="n">
         <v>3</v>
       </c>
       <c r="J202" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K202" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L202" t="n">
-        <v>12.9</v>
+        <v>17.65</v>
       </c>
       <c r="M202" t="n">
         <v>77.83</v>
       </c>
       <c r="N202" t="n">
-        <v>38.4</v>
+        <v>25.6</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -12429,7 +12229,7 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="203">
@@ -12458,38 +12258,38 @@
         <v>6</v>
       </c>
       <c r="G203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Marra Donna (IRE)</t>
+          <t>Barry The Worm</t>
         </is>
       </c>
       <c r="I203" t="n">
         <v>3</v>
       </c>
       <c r="J203" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K203" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L203" t="n">
-        <v>17.65</v>
+        <v>21.4</v>
       </c>
       <c r="M203" t="n">
         <v>77.83</v>
       </c>
       <c r="N203" t="n">
-        <v>25.6</v>
+        <v>35.4</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P203" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -12518,11 +12318,11 @@
         <v>6</v>
       </c>
       <c r="G204" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Barry The Worm</t>
+          <t>Grand Vista (IRE)</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -12535,13 +12335,13 @@
         <v>60</v>
       </c>
       <c r="L204" t="n">
-        <v>21.4</v>
+        <v>26.15</v>
       </c>
       <c r="M204" t="n">
         <v>77.83</v>
       </c>
       <c r="N204" t="n">
-        <v>35.4</v>
+        <v>30.9</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -12577,40 +12377,24 @@
       <c r="F205" t="n">
         <v>6</v>
       </c>
-      <c r="G205" t="n">
-        <v>11</v>
-      </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Grand Vista (IRE)</t>
-        </is>
-      </c>
-      <c r="I205" t="n">
-        <v>3</v>
-      </c>
-      <c r="J205" t="n">
-        <v>131</v>
-      </c>
-      <c r="K205" t="n">
-        <v>60</v>
-      </c>
-      <c r="L205" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="M205" t="n">
-        <v>77.83</v>
-      </c>
-      <c r="N205" t="n">
-        <v>30.9</v>
-      </c>
+          <t>Thats Random</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P205" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
